--- a/figs_data/fig_3_data/fig_3_analysis/human_eval_template.xlsx
+++ b/figs_data/fig_3_data/fig_3_analysis/human_eval_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\github_remotes\FlowMOP\figs_data\fig_3_data\fig_3_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="repository/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854582D7-E3E3-46BD-AF38-46129A127C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
